--- a/PowerQuery-and-PowerPivot/Power-Query/MergeData-of-Sheets/ProductData.xlsx
+++ b/PowerQuery-and-PowerPivot/Power-Query/MergeData-of-Sheets/ProductData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit\Excel_Practice\PowerQuery-and-PowerPivot\Power-Query\MergeData-of-Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FA664A-F5A4-4953-9861-92488E5143B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32245D72-5CAE-42C9-B88F-C64BD3CC1B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{C027AD67-E6A1-45FC-9CE8-3B885CEE3DBD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" activeTab="1" xr2:uid="{C027AD67-E6A1-45FC-9CE8-3B885CEE3DBD}"/>
   </bookViews>
   <sheets>
     <sheet name="FactDimension-MergedData" sheetId="5" r:id="rId1"/>
@@ -942,15 +942,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1246,6 +1237,15 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1262,6 +1262,116 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>535780</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142873</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>501926</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>154779</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C36DEDEF-2F6C-2CE8-6123-DFA474E83A95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13477874" y="1035842"/>
+          <a:ext cx="7252771" cy="3762375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>540776</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>180260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>90130</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>60836</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAF90AFB-2FBB-4357-B312-A95B6CF15668}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8955550" y="1687873"/>
+          <a:ext cx="5612580" cy="2895802"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1289,43 +1399,43 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5AF703A2-2157-4974-BCDD-517263030F1D}" uniqueName="1" name="Transaction_ID" queryTableFieldId="1" dataDxfId="25"/>
     <tableColumn id="2" xr3:uid="{D52C0ED4-415F-49DD-A72F-7ACD00FC3CE3}" uniqueName="2" name="Product_ID" queryTableFieldId="2" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{6BFB30BD-6C43-450A-A6AC-F062D35B16E8}" uniqueName="7" name="Product_Name" queryTableFieldId="7" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{8D0E313F-F832-406C-B237-27F24623AAE9}" uniqueName="8" name="Category" queryTableFieldId="8" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{E6F33B19-38F6-4C53-8FC2-32051F07D242}" uniqueName="3" name="Production_Date" queryTableFieldId="3" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{6BFB30BD-6C43-450A-A6AC-F062D35B16E8}" uniqueName="7" name="Product_Name" queryTableFieldId="7" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{8D0E313F-F832-406C-B237-27F24623AAE9}" uniqueName="8" name="Category" queryTableFieldId="8" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{E6F33B19-38F6-4C53-8FC2-32051F07D242}" uniqueName="3" name="Production_Date" queryTableFieldId="3" dataDxfId="21"/>
     <tableColumn id="4" xr3:uid="{A65D0C32-625C-4ECC-ABE6-C8DDAE5E0966}" uniqueName="4" name="Units_Produced" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{D47FB148-2376-4587-A66F-54E43051099C}" uniqueName="5" name="Total_Cost" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{633DDBEB-5FC2-4810-99A3-B6D21FFE28F0}" uniqueName="6" name="Factory_Name" queryTableFieldId="6" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{633DDBEB-5FC2-4810-99A3-B6D21FFE28F0}" uniqueName="6" name="Factory_Name" queryTableFieldId="6" dataDxfId="20"/>
     <tableColumn id="9" xr3:uid="{4998BEFB-9FA8-496F-A5EA-B3879FDCC8A9}" uniqueName="9" name="Unit_Price" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{F1C6190F-4B0E-442E-95D0-96EF5FAFAA9A}" uniqueName="10" name="Supplier" queryTableFieldId="10" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{F1C6190F-4B0E-442E-95D0-96EF5FAFAA9A}" uniqueName="10" name="Supplier" queryTableFieldId="10" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09D3297B-2BB1-4D00-B4A5-D34F5C9CA707}" name="Table1" displayName="Table1" ref="A1:F101" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09D3297B-2BB1-4D00-B4A5-D34F5C9CA707}" name="Table1" displayName="Table1" ref="A1:F101" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:F101" xr:uid="{09D3297B-2BB1-4D00-B4A5-D34F5C9CA707}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E7579689-F933-4253-ABDD-1AE8E965C0C8}" name="Transaction_ID" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{775AD574-52B3-4046-8C74-F55575687EB9}" name="Product_ID" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{061E2CE8-F56E-443E-A34F-37235D2EDE84}" name="Production_Date" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{5107D65B-7180-4DF9-B3B9-59BE9FCCA154}" name="Units_Produced" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{68C72F5B-FC7B-4537-96D6-B518B6B4A9C6}" name="Total_Cost" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{A5628965-ED29-42B2-8FA0-5D172941F9E7}" name="Factory_Name" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{E7579689-F933-4253-ABDD-1AE8E965C0C8}" name="Transaction_ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{775AD574-52B3-4046-8C74-F55575687EB9}" name="Product_ID" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{061E2CE8-F56E-443E-A34F-37235D2EDE84}" name="Production_Date" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{5107D65B-7180-4DF9-B3B9-59BE9FCCA154}" name="Units_Produced" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{68C72F5B-FC7B-4537-96D6-B518B6B4A9C6}" name="Total_Cost" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{A5628965-ED29-42B2-8FA0-5D172941F9E7}" name="Factory_Name" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{404DFB27-4D81-40EC-96B2-7CE110378418}" name="Table2" displayName="Table2" ref="A1:E26" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{404DFB27-4D81-40EC-96B2-7CE110378418}" name="Table2" displayName="Table2" ref="A1:E26" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E26" xr:uid="{404DFB27-4D81-40EC-96B2-7CE110378418}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B84811EF-00A9-4D9D-A75F-0563577859A1}" name="Product_ID" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{4E12B7FB-9AC4-411A-9D0E-E8376FBFA902}" name="Product_Name" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{F61DD5C2-3C4E-47D1-BEC4-543F7491B804}" name="Category" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{36444FE1-BC0E-4E66-ADE8-C4CE27724F22}" name="Unit_Price" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9039E279-F69D-4A1C-ADA5-CF0061A08C09}" name="Supplier" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{B84811EF-00A9-4D9D-A75F-0563577859A1}" name="Product_ID" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{4E12B7FB-9AC4-411A-9D0E-E8376FBFA902}" name="Product_Name" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F61DD5C2-3C4E-47D1-BEC4-543F7491B804}" name="Category" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{36444FE1-BC0E-4E66-ADE8-C4CE27724F22}" name="Unit_Price" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{9039E279-F69D-4A1C-ADA5-CF0061A08C09}" name="Supplier" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4880,8 +4990,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6921,8 +7032,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
